--- a/backend/ai_vs_ai_results.xlsx
+++ b/backend/ai_vs_ai_results.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Per AI Detail" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Matchups" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Head to Head" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Per AI Detail" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Matchups" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Head to Head" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Summary'!$A$1:$G$5</definedName>
@@ -524,7 +524,7 @@
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="9" customWidth="1" min="5" max="5"/>
     <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -574,19 +574,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0.8</v>
+        <v>0.8333333333333334</v>
       </c>
     </row>
     <row r="3">
@@ -599,19 +599,19 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G3" s="7" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="4">
@@ -624,19 +624,19 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.3666666666666666</v>
       </c>
     </row>
     <row r="5">
@@ -649,13 +649,13 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>0</v>
@@ -685,7 +685,7 @@
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="9" customWidth="1" min="5" max="5"/>
     <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -737,13 +737,13 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>0</v>
@@ -764,13 +764,13 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>0</v>
@@ -791,13 +791,13 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>0</v>
@@ -818,13 +818,13 @@
         </is>
       </c>
       <c r="C5" s="10" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="D5" s="10" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="10" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="F5" s="10" t="n">
         <v>0</v>
@@ -845,10 +845,10 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E6" s="5" t="n">
         <v>0</v>
@@ -872,19 +872,19 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F7" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="8">
@@ -899,19 +899,19 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F8" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -926,19 +926,19 @@
         </is>
       </c>
       <c r="C9" s="10" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="D9" s="10" t="n">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="F9" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G9" s="11" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.3666666666666666</v>
       </c>
     </row>
     <row r="10">
@@ -953,10 +953,10 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>0</v>
@@ -980,19 +980,19 @@
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="12">
@@ -1007,19 +1007,19 @@
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="13">
@@ -1034,19 +1034,19 @@
         </is>
       </c>
       <c r="C13" s="10" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="D13" s="10" t="n">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="E13" s="10" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="F13" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G13" s="11" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="14">
@@ -1061,10 +1061,10 @@
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E14" s="5" t="n">
         <v>0</v>
@@ -1088,19 +1088,19 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F15" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1115,19 +1115,19 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F16" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G16" s="7" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="17">
@@ -1142,19 +1142,19 @@
         </is>
       </c>
       <c r="C17" s="10" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="D17" s="10" t="n">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="E17" s="10" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="F17" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G17" s="11" t="n">
-        <v>0.8</v>
+        <v>0.8333333333333334</v>
       </c>
     </row>
   </sheetData>
@@ -1258,13 +1258,13 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>0</v>
@@ -1276,10 +1276,10 @@
         <v>1</v>
       </c>
       <c r="J2" s="13" t="n">
-        <v>52.2</v>
+        <v>50.7</v>
       </c>
       <c r="K2" s="13" t="n">
-        <v>52.7</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="3">
@@ -1299,13 +1299,13 @@
         </is>
       </c>
       <c r="D3" s="5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E3" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G3" s="5" t="n">
         <v>0</v>
@@ -1317,10 +1317,10 @@
         <v>1</v>
       </c>
       <c r="J3" s="14" t="n">
-        <v>44.3</v>
+        <v>46</v>
       </c>
       <c r="K3" s="14" t="n">
-        <v>44.8</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="4">
@@ -1340,13 +1340,13 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>0</v>
@@ -1358,10 +1358,10 @@
         <v>1</v>
       </c>
       <c r="J4" s="13" t="n">
-        <v>40.55</v>
+        <v>38.7</v>
       </c>
       <c r="K4" s="13" t="n">
-        <v>41.05</v>
+        <v>39.2</v>
       </c>
     </row>
     <row r="5">
@@ -1381,28 +1381,28 @@
         </is>
       </c>
       <c r="D5" s="5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="I5" s="7" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J5" s="14" t="n">
-        <v>41.1</v>
+        <v>43.9</v>
       </c>
       <c r="K5" s="14" t="n">
-        <v>41.2</v>
+        <v>44.3</v>
       </c>
     </row>
     <row r="6">
@@ -1422,28 +1422,28 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J6" s="13" t="n">
-        <v>43.8</v>
+        <v>42.3</v>
       </c>
       <c r="K6" s="13" t="n">
-        <v>44.1</v>
+        <v>42.8</v>
       </c>
     </row>
     <row r="7">
@@ -1463,28 +1463,28 @@
         </is>
       </c>
       <c r="D7" s="5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="G7" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="I7" s="7" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J7" s="14" t="n">
-        <v>39.15</v>
+        <v>36.7</v>
       </c>
       <c r="K7" s="14" t="n">
-        <v>39.25</v>
+        <v>36.7</v>
       </c>
     </row>
   </sheetData>
@@ -1613,7 +1613,7 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C4" s="17" t="inlineStr">
         <is>
@@ -1621,10 +1621,10 @@
         </is>
       </c>
       <c r="D4" s="5" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G4" s="7" t="n">
         <v>1</v>
@@ -1635,10 +1635,10 @@
         </is>
       </c>
       <c r="I4" s="7" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="J4" s="7" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D5" s="17" t="inlineStr">
         <is>
@@ -1659,13 +1659,13 @@
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G5" s="4" t="n">
         <v>1</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="I5" s="17" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         </is>
       </c>
       <c r="J5" s="4" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="6">
@@ -1683,13 +1683,13 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E6" s="17" t="inlineStr">
         <is>
@@ -1700,10 +1700,10 @@
         <v>1</v>
       </c>
       <c r="H6" s="7" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J6" s="17" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
     <row r="8">
       <c r="A8" s="18" t="inlineStr">
         <is>
-          <t>Win rate = games won / (won + lost); drawn games excluded. 20 games per match-up, starting player alternated.</t>
+          <t>Win rate = games won / (won + lost); drawn games excluded. 10 games per match-up, starting player alternated.</t>
         </is>
       </c>
     </row>
